--- a/data/Mörel-Filet/investment_decision/Breiten_SFH_until_2004_investment_decision.xlsx
+++ b/data/Mörel-Filet/investment_decision/Breiten_SFH_until_2004_investment_decision.xlsx
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>414.7668856986576</v>
+        <v>229.2642736585352</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>57373.96166215032</v>
       </c>
       <c r="F2" t="n">
-        <v>410.3987263490191</v>
+        <v>229.2642736585352</v>
       </c>
       <c r="G2" t="n">
         <v>57373.96166215032</v>
       </c>
       <c r="H2" t="n">
-        <v>399.0684889543511</v>
+        <v>229.2642736585352</v>
       </c>
       <c r="I2" t="n">
         <v>57373.96166215032</v>
       </c>
       <c r="J2" t="n">
-        <v>409.8527855677246</v>
+        <v>229.2642736585351</v>
       </c>
       <c r="K2" t="n">
         <v>57373.96166215032</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>414.7668856986576</v>
+        <v>232.0946477181273</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>57373.96166215032</v>
       </c>
       <c r="F3" t="n">
-        <v>410.3987263490191</v>
+        <v>229.2642736585352</v>
       </c>
       <c r="G3" t="n">
         <v>57373.96166215032</v>
       </c>
       <c r="H3" t="n">
-        <v>399.0684889543511</v>
+        <v>229.2642736585352</v>
       </c>
       <c r="I3" t="n">
         <v>57373.96166215032</v>
       </c>
       <c r="J3" t="n">
-        <v>409.8527855677246</v>
+        <v>231.3354275474743</v>
       </c>
       <c r="K3" t="n">
         <v>57373.96166215032</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>414.7668856986576</v>
+        <v>232.0946477181273</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>57373.96166215032</v>
       </c>
       <c r="F4" t="n">
-        <v>410.3987263490191</v>
+        <v>229.2642736585352</v>
       </c>
       <c r="G4" t="n">
         <v>57373.96166215032</v>
       </c>
       <c r="H4" t="n">
-        <v>399.068488954351</v>
+        <v>229.2642736585352</v>
       </c>
       <c r="I4" t="n">
         <v>57373.96166215032</v>
       </c>
       <c r="J4" t="n">
-        <v>409.8527855677246</v>
+        <v>231.3354275474743</v>
       </c>
       <c r="K4" t="n">
         <v>57373.96166215032</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>414.7668856986576</v>
+        <v>232.0946477181273</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>57373.96166215032</v>
       </c>
       <c r="F5" t="n">
-        <v>410.3987263490191</v>
+        <v>229.2642736585352</v>
       </c>
       <c r="G5" t="n">
         <v>57373.96166215032</v>
       </c>
       <c r="H5" t="n">
-        <v>399.0684889543511</v>
+        <v>229.2642736585352</v>
       </c>
       <c r="I5" t="n">
         <v>57373.96166215032</v>
       </c>
       <c r="J5" t="n">
-        <v>409.8527855677246</v>
+        <v>231.3354275474743</v>
       </c>
       <c r="K5" t="n">
         <v>57373.96166215032</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>414.7668856986576</v>
+        <v>232.0946477181273</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>57373.96166215032</v>
       </c>
       <c r="F6" t="n">
-        <v>410.3987263490191</v>
+        <v>229.2642736585352</v>
       </c>
       <c r="G6" t="n">
         <v>57373.96166215032</v>
       </c>
       <c r="H6" t="n">
-        <v>399.0684889543511</v>
+        <v>229.2642736585352</v>
       </c>
       <c r="I6" t="n">
         <v>57373.96166215032</v>
       </c>
       <c r="J6" t="n">
-        <v>409.8527855677246</v>
+        <v>231.3354275474743</v>
       </c>
       <c r="K6" t="n">
         <v>57373.96166215032</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Breiten_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Breiten_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>86.06094249322548</v>
+        <v>64.86683865168538</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>86.06094249322548</v>
+        <v>64.86683865168538</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>49.41912355816649</v>
+        <v>37.24874747226516</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>49.41912355816649</v>
+        <v>37.24874747226516</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Breiten_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Breiten_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>86.06094249322548</v>
+        <v>64.86683865168538</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>86.06094249322548</v>
+        <v>64.86683865168538</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>63.90842748506472</v>
+        <v>48.16979147634777</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>63.90842748506472</v>
+        <v>48.16979147634777</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Breiten_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Breiten_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>86.06094249322548</v>
+        <v>64.86683865168538</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>86.06094249322548</v>
+        <v>64.86683865168538</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>70.36113541498138</v>
+        <v>53.03340035663982</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>70.36113541498138</v>
+        <v>53.03340035663982</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Breiten_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Breiten_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>86.06094249322548</v>
+        <v>64.86683865168538</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>86.06094249322548</v>
+        <v>64.86683865168538</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>73.89705098473033</v>
+        <v>55.69853111287041</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>73.89705098473033</v>
+        <v>55.69853111287041</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Breiten_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Breiten_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>86.06094249322548</v>
+        <v>64.86683865168538</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>86.06094249322548</v>
+        <v>64.86683865168538</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>76.09244119276377</v>
+        <v>57.35326574947057</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>76.09244119276377</v>
+        <v>57.35326574947057</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01004236780235294</v>
+        <v>0.009605743115294118</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01004236780235294</v>
+        <v>0.009605743115294118</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01004236780235294</v>
+        <v>0.009605743115294118</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01004236780235294</v>
+        <v>0.009605743115294118</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01004236780235294</v>
+        <v>0.009605743115294118</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01004236780235294</v>
+        <v>0.009605743115294118</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01004236780235294</v>
+        <v>0.009605743115294118</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01004236780235294</v>
+        <v>0.009605743115294118</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01178886655058824</v>
+        <v>0.01004236780235294</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01178886655058824</v>
+        <v>0.01004236780235294</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01178886655058824</v>
+        <v>0.01004236780235294</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01178886655058824</v>
+        <v>0.01004236780235294</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01178886655058824</v>
+        <v>0.01004236780235294</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01178886655058824</v>
+        <v>0.01004236780235294</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01178886655058824</v>
+        <v>0.01004236780235294</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01178886655058824</v>
+        <v>0.01004236780235294</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01178886655058824</v>
+        <v>0.01004236780235294</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01178886655058824</v>
+        <v>0.01004236780235294</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01178886655058824</v>
+        <v>0.01004236780235294</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01178886655058824</v>
+        <v>0.01004236780235294</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.9278274600000007</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>7.793750664000002</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.9278274600000007</v>
       </c>
       <c r="G19" t="n">
         <v>7.793750664000002</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.9278274600000007</v>
       </c>
       <c r="I19" t="n">
         <v>7.793750664000002</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.9278274600000007</v>
       </c>
       <c r="K19" t="n">
         <v>7.793750664000002</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.9278274600000007</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>7.793750664000002</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.9278274600000007</v>
       </c>
       <c r="G20" t="n">
         <v>7.793750664000002</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.9278274600000007</v>
       </c>
       <c r="I20" t="n">
         <v>7.793750664000002</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.9278274600000007</v>
       </c>
       <c r="K20" t="n">
         <v>7.793750664000002</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.9278274600000007</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>7.793750664000002</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.9278274600000007</v>
       </c>
       <c r="G21" t="n">
         <v>7.793750664000002</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.9278274600000007</v>
       </c>
       <c r="I21" t="n">
         <v>7.793750664000002</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.9278274600000007</v>
       </c>
       <c r="K21" t="n">
         <v>7.793750664000002</v>
@@ -2345,7 +2345,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>8.915355047379611</v>
+        <v>8.058426848471219</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2359,19 +2359,19 @@
         <v>89.01784408038868</v>
       </c>
       <c r="F52" t="n">
-        <v>6.628897618351087</v>
+        <v>5.818163462783014</v>
       </c>
       <c r="G52" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="H52" t="n">
-        <v>17.73026773721944</v>
+        <v>5.267849550191939</v>
       </c>
       <c r="I52" t="n">
         <v>23.98412643874303</v>
       </c>
       <c r="J52" t="n">
-        <v>18.5354700587178</v>
+        <v>7.354152608594842</v>
       </c>
       <c r="K52" t="n">
         <v>23.98412643874303</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>8.950671008530099</v>
+        <v>9.709553113641794</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>89.01784408038868</v>
       </c>
       <c r="F53" t="n">
-        <v>6.664213579501573</v>
+        <v>7.565076848868664</v>
       </c>
       <c r="G53" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="H53" t="n">
-        <v>17.76558369836993</v>
+        <v>7.014762936277584</v>
       </c>
       <c r="I53" t="n">
         <v>35.38303717682141</v>
       </c>
       <c r="J53" t="n">
-        <v>18.57078601986828</v>
+        <v>9.030972832498909</v>
       </c>
       <c r="K53" t="n">
         <v>35.38303717682141</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>17.95067100853011</v>
+        <v>17.86846577495659</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>89.01784408038868</v>
       </c>
       <c r="F54" t="n">
-        <v>15.66421357950158</v>
+        <v>15.69333950796491</v>
       </c>
       <c r="G54" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="H54" t="n">
-        <v>26.09108315732707</v>
+        <v>15.30518955744621</v>
       </c>
       <c r="I54" t="n">
         <v>41.91852636217848</v>
       </c>
       <c r="J54" t="n">
-        <v>27.43761589528757</v>
+        <v>17.25249158662567</v>
       </c>
       <c r="K54" t="n">
         <v>41.91852636217848</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>29.55160985355982</v>
+        <v>29.12007713200779</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>89.01784408038868</v>
       </c>
       <c r="F55" t="n">
-        <v>28.86070254577468</v>
+        <v>28.5251913807481</v>
       </c>
       <c r="G55" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="H55" t="n">
-        <v>28.89068672929267</v>
+        <v>28.5251913807481</v>
       </c>
       <c r="I55" t="n">
         <v>46.12349983331355</v>
       </c>
       <c r="J55" t="n">
-        <v>29.55160985355983</v>
+        <v>28.99661247604942</v>
       </c>
       <c r="K55" t="n">
         <v>46.12349983331355</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>29.51629389240934</v>
+        <v>28.77293578642868</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>89.01784408038868</v>
       </c>
       <c r="F56" t="n">
-        <v>28.82538658462419</v>
+        <v>28.19078506678298</v>
       </c>
       <c r="G56" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="H56" t="n">
-        <v>28.85537076814218</v>
+        <v>28.19078506678297</v>
       </c>
       <c r="I56" t="n">
         <v>49.04654070683023</v>
       </c>
       <c r="J56" t="n">
-        <v>29.51629389240935</v>
+        <v>28.77957530551674</v>
       </c>
       <c r="K56" t="n">
         <v>49.04654070683023</v>
@@ -2715,7 +2715,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>7.73985812160767</v>
+        <v>0.9575432701486185</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2729,19 +2729,19 @@
         <v>89.01784408038868</v>
       </c>
       <c r="F62" t="n">
-        <v>8.47662910658908</v>
+        <v>2.047479681633898</v>
       </c>
       <c r="G62" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="H62" t="n">
-        <v>9.321309220460675</v>
+        <v>2.113555029507336</v>
       </c>
       <c r="I62" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="J62" t="n">
-        <v>8.278218003079086</v>
+        <v>1.039203802606045</v>
       </c>
       <c r="K62" t="n">
         <v>89.01784408038868</v>
@@ -2752,7 +2752,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>7.73985812160767</v>
+        <v>0.9575432701486185</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2766,19 +2766,19 @@
         <v>89.01784408038868</v>
       </c>
       <c r="F63" t="n">
-        <v>8.47662910658908</v>
+        <v>2.047479681633898</v>
       </c>
       <c r="G63" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="H63" t="n">
-        <v>9.321309220460675</v>
+        <v>2.113555029507336</v>
       </c>
       <c r="I63" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="J63" t="n">
-        <v>8.278218003079086</v>
+        <v>1.039203802606045</v>
       </c>
       <c r="K63" t="n">
         <v>89.01784408038868</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>7.73985812160767</v>
+        <v>3.663968316672289</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>89.01784408038868</v>
       </c>
       <c r="F64" t="n">
-        <v>8.47662910658908</v>
+        <v>4.713519747669887</v>
       </c>
       <c r="G64" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="H64" t="n">
-        <v>9.995809761503549</v>
+        <v>4.617431133470947</v>
       </c>
       <c r="I64" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="J64" t="n">
-        <v>8.411388127659812</v>
+        <v>3.663968316672293</v>
       </c>
       <c r="K64" t="n">
         <v>89.01784408038868</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>9.828292139821389</v>
+        <v>6.310272463651535</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>89.01784408038868</v>
       </c>
       <c r="F65" t="n">
-        <v>10.61555590384857</v>
+        <v>6.92991035312008</v>
       </c>
       <c r="G65" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="H65" t="n">
-        <v>10.83550342756589</v>
+        <v>6.929910353120083</v>
       </c>
       <c r="I65" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="J65" t="n">
-        <v>9.936691407415491</v>
+        <v>6.440376638697941</v>
       </c>
       <c r="K65" t="n">
         <v>89.01784408038868</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>15.29038750634578</v>
+        <v>9.801396293737332</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>89.01784408038868</v>
       </c>
       <c r="F66" t="n">
-        <v>16.07765127037295</v>
+        <v>10.41013662207866</v>
       </c>
       <c r="G66" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="H66" t="n">
-        <v>16.29759879409028</v>
+        <v>10.41017852373578</v>
       </c>
       <c r="I66" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="J66" t="n">
-        <v>15.39878677393988</v>
+        <v>9.802067737700128</v>
       </c>
       <c r="K66" t="n">
         <v>89.01784408038868</v>
@@ -3108,13 +3108,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>2.702161333330261</v>
+        <v>89.01784408038868</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>2.702161333330261</v>
+        <v>89.01784408038868</v>
       </c>
     </row>
     <row r="73">
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>4.57643314272564</v>
+        <v>89.01784408038868</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>4.57643314272564</v>
+        <v>89.01784408038868</v>
       </c>
     </row>
     <row r="74">
@@ -3182,13 +3182,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>6.024783743374103</v>
+        <v>89.01784408038868</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>6.024783743374103</v>
+        <v>89.01784408038868</v>
       </c>
     </row>
     <row r="75">
@@ -3219,13 +3219,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>7.202294983587766</v>
+        <v>89.01784408038868</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>7.202294983587766</v>
+        <v>89.01784408038868</v>
       </c>
     </row>
     <row r="76">
@@ -3256,13 +3256,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>8.190657360819399</v>
+        <v>89.01784408038868</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>8.190657360819399</v>
+        <v>89.01784408038868</v>
       </c>
     </row>
     <row r="77">
@@ -3270,7 +3270,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>13.68937286324344</v>
+        <v>13.89791550403045</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3284,22 +3284,22 @@
         <v>89.01784408038868</v>
       </c>
       <c r="F77" t="n">
-        <v>15.33541576353258</v>
+        <v>15.04824247823338</v>
       </c>
       <c r="G77" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="H77" t="n">
-        <v>3.63929723802795</v>
+        <v>15.53248104295102</v>
       </c>
       <c r="I77" t="n">
-        <v>2.702161333330261</v>
+        <v>89.01784408038868</v>
       </c>
       <c r="J77" t="n">
-        <v>3.63929723802795</v>
+        <v>14.5205292114494</v>
       </c>
       <c r="K77" t="n">
-        <v>2.702161333330261</v>
+        <v>89.01784408038868</v>
       </c>
     </row>
     <row r="78">
@@ -3307,7 +3307,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>13.68937286324344</v>
+        <v>13.89791550403045</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3321,22 +3321,22 @@
         <v>89.01784408038868</v>
       </c>
       <c r="F78" t="n">
-        <v>15.33541576353258</v>
+        <v>15.04824247823338</v>
       </c>
       <c r="G78" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="H78" t="n">
-        <v>3.63929723802795</v>
+        <v>15.53248104295102</v>
       </c>
       <c r="I78" t="n">
-        <v>4.57643314272564</v>
+        <v>89.01784408038868</v>
       </c>
       <c r="J78" t="n">
-        <v>3.63929723802795</v>
+        <v>14.5205292114494</v>
       </c>
       <c r="K78" t="n">
-        <v>4.57643314272564</v>
+        <v>89.01784408038868</v>
       </c>
     </row>
     <row r="79">
@@ -3344,7 +3344,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>13.68937286324344</v>
+        <v>13.89791550403045</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3358,22 +3358,22 @@
         <v>89.01784408038868</v>
       </c>
       <c r="F79" t="n">
-        <v>15.33541576353258</v>
+        <v>15.04824247823338</v>
       </c>
       <c r="G79" t="n">
         <v>89.01784408038868</v>
       </c>
       <c r="H79" t="n">
-        <v>3.63929723802795</v>
+        <v>15.53248104295102</v>
       </c>
       <c r="I79" t="n">
-        <v>6.024783743374103</v>
+        <v>89.01784408038868</v>
       </c>
       <c r="J79" t="n">
-        <v>3.63929723802795</v>
+        <v>14.5205292114494</v>
       </c>
       <c r="K79" t="n">
-        <v>6.024783743374103</v>
+        <v>89.01784408038868</v>
       </c>
     </row>
     <row r="80">
@@ -3404,13 +3404,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>7.202294983587766</v>
+        <v>89.01784408038868</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>7.202294983587766</v>
+        <v>89.01784408038868</v>
       </c>
     </row>
     <row r="81">
@@ -3441,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>8.190657360819399</v>
+        <v>89.01784408038868</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>8.190657360819399</v>
+        <v>89.01784408038868</v>
       </c>
     </row>
     <row r="82">
